--- a/output/pdf_financials_xlsx/SEND.xlsx
+++ b/output/pdf_financials_xlsx/SEND.xlsx
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.007379</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0</v>
@@ -1017,7 +1017,7 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.007379</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0</v>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">

--- a/output/pdf_financials_xlsx/SEND.xlsx
+++ b/output/pdf_financials_xlsx/SEND.xlsx
@@ -2515,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>0</v>
+        <v>-1e-06</v>
       </c>
     </row>
     <row r="122">
@@ -3712,7 +3712,11 @@
           <t>Shares repurchased</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
